--- a/registration_forms/038_free_course_preview_lead_form--registration_forms.xlsx
+++ b/registration_forms/038_free_course_preview_lead_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How do you want to be contacted?</t>
+          <t>Select Multiple</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
